--- a/ksoft/docs/records/Cost_Center_Records.xlsx
+++ b/ksoft/docs/records/Cost_Center_Records.xlsx
@@ -3581,13 +3581,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1361CD69-11E1-4E46-B404-F350C6C2C271}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DB5F9D5-7EB6-404C-952A-AD5F63C507ED}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90B2C33-2E8A-4130-9FD2-75DC9D08811D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B54E94C-BE61-4A45-9270-F613C1142C11}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D624441-6FE7-4C74-93D0-2C8F84DC4AB7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D10EE9C-65B3-4B11-8C69-9DF65851E396}"/>
 </file>
--- a/ksoft/docs/records/Cost_Center_Records.xlsx
+++ b/ksoft/docs/records/Cost_Center_Records.xlsx
@@ -3581,13 +3581,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DB5F9D5-7EB6-404C-952A-AD5F63C507ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1361CD69-11E1-4E46-B404-F350C6C2C271}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B54E94C-BE61-4A45-9270-F613C1142C11}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90B2C33-2E8A-4130-9FD2-75DC9D08811D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D10EE9C-65B3-4B11-8C69-9DF65851E396}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D624441-6FE7-4C74-93D0-2C8F84DC4AB7}"/>
 </file>